--- a/final_data_pipeline/output/311942longform_elec_options.xlsx
+++ b/final_data_pipeline/output/311942longform_elec_options.xlsx
@@ -576,7 +576,7 @@
         <v>70</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L2">
         <v>8000</v>
@@ -597,10 +597,10 @@
         <v>4.726875</v>
       </c>
       <c r="R2">
-        <v>1.741590909090909</v>
+        <v>1.837513876759573</v>
       </c>
       <c r="S2">
-        <v>1.89075</v>
+        <v>2.005936573945218</v>
       </c>
       <c r="T2">
         <v>92.35213186775687</v>
@@ -635,7 +635,7 @@
         <v>34</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L3">
         <v>8000</v>
@@ -650,10 +650,10 @@
         <v>77033.05786125691</v>
       </c>
       <c r="R3">
-        <v>1.741590909090909</v>
+        <v>1.837513876759573</v>
       </c>
       <c r="S3">
-        <v>1.89075</v>
+        <v>2.005936573945218</v>
       </c>
       <c r="T3">
         <v>9.629132232657113</v>
@@ -694,7 +694,7 @@
         <v>70</v>
       </c>
       <c r="K4">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="L4">
         <v>8000</v>
@@ -715,10 +715,10 @@
         <v>4.726875</v>
       </c>
       <c r="R4">
-        <v>1.741590909090909</v>
+        <v>1.798225615362447</v>
       </c>
       <c r="S4">
-        <v>1.89075</v>
+        <v>1.958604378795604</v>
       </c>
       <c r="T4">
         <v>33.1126523689186</v>
@@ -753,7 +753,7 @@
         <v>34</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="L5">
         <v>8000</v>
@@ -768,10 +768,10 @@
         <v>27620.03230772358</v>
       </c>
       <c r="R5">
-        <v>1.741590909090909</v>
+        <v>1.798225615362447</v>
       </c>
       <c r="S5">
-        <v>1.89075</v>
+        <v>1.958604378795604</v>
       </c>
       <c r="T5">
         <v>3.452504038465447</v>
@@ -812,7 +812,7 @@
         <v>70</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="L6">
         <v>8000</v>
@@ -833,10 +833,10 @@
         <v>4.726875</v>
       </c>
       <c r="R6">
-        <v>1.741590909090909</v>
+        <v>1.894871325212932</v>
       </c>
       <c r="S6">
-        <v>1.89075</v>
+        <v>2.075424331741031</v>
       </c>
       <c r="T6">
         <v>92.53961146453506</v>
@@ -871,7 +871,7 @@
         <v>34</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>18.89814814814816</v>
       </c>
       <c r="L7">
         <v>8000</v>
@@ -886,10 +886,10 @@
         <v>77189.43894672119</v>
       </c>
       <c r="R7">
-        <v>1.741590909090909</v>
+        <v>1.894871325212932</v>
       </c>
       <c r="S7">
-        <v>1.89075</v>
+        <v>2.075424331741031</v>
       </c>
       <c r="T7">
         <v>9.648679868340148</v>
@@ -930,7 +930,7 @@
         <v>70</v>
       </c>
       <c r="K8">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="L8">
         <v>8000</v>
@@ -951,10 +951,10 @@
         <v>4.726875</v>
       </c>
       <c r="R8">
-        <v>1.741590909090909</v>
+        <v>1.798225615362447</v>
       </c>
       <c r="S8">
-        <v>1.89075</v>
+        <v>1.958604378795604</v>
       </c>
       <c r="T8">
         <v>80.06989677374054</v>
@@ -989,7 +989,7 @@
         <v>34</v>
       </c>
       <c r="K9">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="L9">
         <v>8000</v>
@@ -1004,10 +1004,10 @@
         <v>66788.16034207742</v>
       </c>
       <c r="R9">
-        <v>1.741590909090909</v>
+        <v>1.798225615362447</v>
       </c>
       <c r="S9">
-        <v>1.89075</v>
+        <v>1.958604378795604</v>
       </c>
       <c r="T9">
         <v>8.348520042759677</v>
@@ -1284,7 +1284,7 @@
         <v>70</v>
       </c>
       <c r="K14">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L14">
         <v>8000</v>
@@ -1305,10 +1305,10 @@
         <v>4.726875</v>
       </c>
       <c r="R14">
-        <v>1.741590909090909</v>
+        <v>1.837513876759573</v>
       </c>
       <c r="S14">
-        <v>1.89075</v>
+        <v>2.005936573945218</v>
       </c>
       <c r="T14">
         <v>167.1064184480875</v>
@@ -1343,7 +1343,7 @@
         <v>34</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L15">
         <v>8000</v>
@@ -1358,10 +1358,10 @@
         <v>139387.3442979308</v>
       </c>
       <c r="R15">
-        <v>1.741590909090909</v>
+        <v>1.837513876759573</v>
       </c>
       <c r="S15">
-        <v>1.89075</v>
+        <v>2.005936573945218</v>
       </c>
       <c r="T15">
         <v>17.42341803724135</v>
@@ -1402,7 +1402,7 @@
         <v>70</v>
       </c>
       <c r="K16">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="L16">
         <v>8000</v>
@@ -1423,10 +1423,10 @@
         <v>4.726875</v>
       </c>
       <c r="R16">
-        <v>1.741590909090909</v>
+        <v>1.940636870984383</v>
       </c>
       <c r="S16">
-        <v>1.89075</v>
+        <v>2.131200751448103</v>
       </c>
       <c r="T16">
         <v>76.44754507803351</v>
@@ -1461,7 +1461,7 @@
         <v>34</v>
       </c>
       <c r="K17">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="L17">
         <v>8000</v>
@@ -1476,10 +1476,10 @@
         <v>63766.67267172464</v>
       </c>
       <c r="R17">
-        <v>1.741590909090909</v>
+        <v>1.940636870984383</v>
       </c>
       <c r="S17">
-        <v>1.89075</v>
+        <v>2.131200751448103</v>
       </c>
       <c r="T17">
         <v>7.97083408396558</v>
@@ -1520,7 +1520,7 @@
         <v>70</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L18">
         <v>8000</v>
@@ -1541,10 +1541,10 @@
         <v>4.726875</v>
       </c>
       <c r="R18">
-        <v>1.741590909090909</v>
+        <v>1.837513876759573</v>
       </c>
       <c r="S18">
-        <v>1.89075</v>
+        <v>2.005936573945218</v>
       </c>
       <c r="T18">
         <v>68.4547065439685</v>
@@ -1579,7 +1579,7 @@
         <v>34</v>
       </c>
       <c r="K19">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L19">
         <v>8000</v>
@@ -1594,10 +1594,10 @@
         <v>57099.66043477941</v>
       </c>
       <c r="R19">
-        <v>1.741590909090909</v>
+        <v>1.837513876759573</v>
       </c>
       <c r="S19">
-        <v>1.89075</v>
+        <v>2.005936573945218</v>
       </c>
       <c r="T19">
         <v>7.137457554347426</v>
